--- a/research/traditional_assets/database/data/pakistan/pakistan_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_office_equipment_services.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.6859999999999999</v>
+        <v>-0.8320000000000001</v>
       </c>
       <c r="G2">
-        <v>1.337370242214533</v>
+        <v>-8.136363636363637</v>
       </c>
       <c r="H2">
-        <v>1.337370242214533</v>
+        <v>-8.136363636363637</v>
       </c>
       <c r="I2">
-        <v>0.6228373702422145</v>
+        <v>-9.954545454545455</v>
       </c>
       <c r="J2">
-        <v>0.5291776153185732</v>
+        <v>-8.645357604480827</v>
       </c>
       <c r="K2">
-        <v>147</v>
+        <v>3.67</v>
       </c>
       <c r="L2">
-        <v>254.325259515571</v>
+        <v>166.8181818181818</v>
       </c>
       <c r="M2">
-        <v>11.7</v>
+        <v>0.321</v>
       </c>
       <c r="N2">
-        <v>0.03209876543209876</v>
+        <v>0.001228943338437979</v>
       </c>
       <c r="O2">
-        <v>0.07959183673469387</v>
+        <v>0.08746594005449591</v>
       </c>
       <c r="P2">
-        <v>11.7</v>
+        <v>0.321</v>
       </c>
       <c r="Q2">
-        <v>0.03209876543209876</v>
+        <v>0.001228943338437979</v>
       </c>
       <c r="R2">
-        <v>0.07959183673469387</v>
+        <v>0.08746594005449591</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,31 +633,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.55</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V2">
-        <v>0.004252400548696845</v>
+        <v>0.0002641653905053599</v>
       </c>
       <c r="W2">
-        <v>1.220930232558139</v>
+        <v>0.01384383251603168</v>
       </c>
       <c r="X2">
-        <v>0.1248606366296094</v>
+        <v>0.1967398531263989</v>
       </c>
       <c r="Y2">
-        <v>1.09606959592853</v>
+        <v>-0.1828960206103672</v>
       </c>
       <c r="Z2">
-        <v>0.004801501923092898</v>
+        <v>8.347562132422689e-05</v>
       </c>
       <c r="AA2">
-        <v>0.002540847337609843</v>
+        <v>-0.000721676597604167</v>
       </c>
       <c r="AB2">
-        <v>0.1248606366296094</v>
+        <v>0.1967398531263989</v>
       </c>
       <c r="AC2">
-        <v>-0.1223197892919996</v>
+        <v>-0.1974615297240031</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.55</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.004270560683289709</v>
+        <v>-0.0002642351922981186</v>
       </c>
       <c r="AK2">
-        <v>-0.005881236956934168</v>
+        <v>-0.0002667893639973553</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-4.305555555555556</v>
+        <v>0.315068493150685</v>
       </c>
     </row>
     <row r="3">
@@ -713,43 +713,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.6859999999999999</v>
+        <v>-0.8320000000000001</v>
       </c>
       <c r="G3">
-        <v>1.337370242214533</v>
+        <v>-8.136363636363637</v>
       </c>
       <c r="H3">
-        <v>1.337370242214533</v>
+        <v>-8.136363636363637</v>
       </c>
       <c r="I3">
-        <v>0.6228373702422145</v>
+        <v>-9.954545454545455</v>
       </c>
       <c r="J3">
-        <v>0.5291776153185732</v>
+        <v>-8.645357604480827</v>
       </c>
       <c r="K3">
-        <v>147</v>
+        <v>3.67</v>
       </c>
       <c r="L3">
-        <v>254.325259515571</v>
+        <v>166.8181818181818</v>
       </c>
       <c r="M3">
-        <v>11.7</v>
+        <v>0.321</v>
       </c>
       <c r="N3">
-        <v>0.03209876543209876</v>
+        <v>0.001228943338437979</v>
       </c>
       <c r="O3">
-        <v>0.07959183673469387</v>
+        <v>0.08746594005449591</v>
       </c>
       <c r="P3">
-        <v>11.7</v>
+        <v>0.321</v>
       </c>
       <c r="Q3">
-        <v>0.03209876543209876</v>
+        <v>0.001228943338437979</v>
       </c>
       <c r="R3">
-        <v>0.07959183673469387</v>
+        <v>0.08746594005449591</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.55</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V3">
-        <v>0.004252400548696845</v>
+        <v>0.0002641653905053599</v>
       </c>
       <c r="W3">
-        <v>1.220930232558139</v>
+        <v>0.01384383251603168</v>
       </c>
       <c r="X3">
-        <v>0.1248606366296094</v>
+        <v>0.1967398531263989</v>
       </c>
       <c r="Y3">
-        <v>1.09606959592853</v>
+        <v>-0.1828960206103672</v>
       </c>
       <c r="Z3">
-        <v>0.004801501923092898</v>
+        <v>8.347562132422689e-05</v>
       </c>
       <c r="AA3">
-        <v>0.002540847337609843</v>
+        <v>-0.000721676597604167</v>
       </c>
       <c r="AB3">
-        <v>0.1248606366296094</v>
+        <v>0.1967398531263989</v>
       </c>
       <c r="AC3">
-        <v>-0.1223197892919996</v>
+        <v>-0.1974615297240031</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.55</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.004270560683289709</v>
+        <v>-0.0002642351922981186</v>
       </c>
       <c r="AK3">
-        <v>-0.005881236956934168</v>
+        <v>-0.0002667893639973553</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP3">
-        <v>-4.305555555555556</v>
+        <v>0.315068493150685</v>
       </c>
     </row>
   </sheetData>
